--- a/docs/Pinouts.xlsx
+++ b/docs/Pinouts.xlsx
@@ -1,38 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Documents\01_Projects\06_ORBIT\open-robotics\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3C9DB9A-5433-410F-8AA3-572D50E098BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63884607-FFB1-4397-A740-F1E320D96561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5820" yWindow="2745" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Standard Pins" sheetId="13" r:id="rId1"/>
-    <sheet name="All Pins" sheetId="1" r:id="rId2"/>
-    <sheet name="Default Pins" sheetId="2" r:id="rId3"/>
-    <sheet name="BLEJoystickController Pins" sheetId="3" r:id="rId4"/>
-    <sheet name="AnalogToDigital" sheetId="4" r:id="rId5"/>
-    <sheet name="BLESingleJoystick" sheetId="12" r:id="rId6"/>
-    <sheet name=" Brain Pins" sheetId="5" r:id="rId7"/>
-    <sheet name="RCCar Pins" sheetId="6" r:id="rId8"/>
-    <sheet name="Robot" sheetId="11" r:id="rId9"/>
-    <sheet name="Crawler" sheetId="10" r:id="rId10"/>
-    <sheet name="Touch LED TFTILI9341" sheetId="7" r:id="rId11"/>
-    <sheet name="Screen ST7735" sheetId="9" r:id="rId12"/>
-    <sheet name="DRV8833 Motor Driver" sheetId="8" r:id="rId13"/>
+    <sheet name="Robot (2)" sheetId="15" r:id="rId1"/>
+    <sheet name="Standard Pins" sheetId="13" r:id="rId2"/>
+    <sheet name="All Pins" sheetId="1" r:id="rId3"/>
+    <sheet name="Default Pins" sheetId="2" r:id="rId4"/>
+    <sheet name="BLEJoystickController Pins" sheetId="3" r:id="rId5"/>
+    <sheet name="AnalogToDigital" sheetId="4" r:id="rId6"/>
+    <sheet name="BLESingleJoystick" sheetId="12" r:id="rId7"/>
+    <sheet name=" Brain Pins" sheetId="5" r:id="rId8"/>
+    <sheet name="RCCar Pins" sheetId="6" r:id="rId9"/>
+    <sheet name="Robot" sheetId="11" r:id="rId10"/>
+    <sheet name="Crawler" sheetId="10" r:id="rId11"/>
+    <sheet name="Touch LED TFTILI9341" sheetId="7" r:id="rId12"/>
+    <sheet name="Screen ST7735" sheetId="9" r:id="rId13"/>
+    <sheet name="DRV8833 Motor Driver" sheetId="8" r:id="rId14"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="230">
   <si>
     <t>LEFT</t>
   </si>
@@ -707,6 +708,21 @@
   </si>
   <si>
     <t>Analog 2</t>
+  </si>
+  <si>
+    <t>Check Servo number</t>
+  </si>
+  <si>
+    <t>Right Joystick</t>
+  </si>
+  <si>
+    <t>Left Joystick</t>
+  </si>
+  <si>
+    <t>L Joystick</t>
+  </si>
+  <si>
+    <t>R Joystick</t>
   </si>
 </sst>
 </file>
@@ -1502,10 +1518,9 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1513,18 +1528,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1775,6 +1791,2811 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937775DF-1B9C-42AD-BAA8-1A440A974685}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
+      <c r="K1" s="71" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="115" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="116"/>
+      <c r="B3" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="K3" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="L3" s="71"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
+        <v>3</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="108"/>
+      <c r="K4" s="70" t="s">
+        <v>80</v>
+      </c>
+      <c r="L4" s="70" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="106" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="7">
+        <v>4</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="K5" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="L5" s="70" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="107"/>
+      <c r="D6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="7">
+        <v>5</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="I6" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="K6" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="L6" s="70" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="7">
+        <v>6</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="K7" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="7">
+        <v>7</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="69" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="69" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
+        <v>8</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="K9" s="71" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="7">
+        <v>9</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="69" t="s">
+        <v>220</v>
+      </c>
+      <c r="I10" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="K10" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="L10" s="70" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="69" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="114"/>
+      <c r="D11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="7">
+        <v>10</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="69" t="s">
+        <v>219</v>
+      </c>
+      <c r="I11" s="125"/>
+      <c r="K11" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="28"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="7">
+        <v>11</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="K12" s="76" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="C13" s="108"/>
+      <c r="D13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
+        <v>13</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="75"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="106" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="7">
+        <v>14</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="106" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="106" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="77" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="108"/>
+      <c r="B16" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="107"/>
+      <c r="D16" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="7">
+        <v>15</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="108"/>
+      <c r="H16" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="112"/>
+      <c r="K16" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="107"/>
+      <c r="D17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="7">
+        <v>16</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="28"/>
+      <c r="K17" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="108"/>
+      <c r="B18" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="108"/>
+      <c r="D18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="7">
+        <v>17</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="28"/>
+      <c r="K18" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
+        <v>18</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="K19" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="L19" s="70" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="127" t="s">
+        <v>199</v>
+      </c>
+      <c r="B20" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="7">
+        <v>19</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="128"/>
+      <c r="B21" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="7">
+        <v>20</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="K21" s="71" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="K22" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="70" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="C23" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="K23" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="L23" s="70" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="C24" s="29"/>
+      <c r="D24" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" s="30"/>
+      <c r="H24" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="K24" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="C25" s="31"/>
+      <c r="D25" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="K25" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="L25" s="70" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="C26" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="C27" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="7">
+        <v>3</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="65"/>
+      <c r="H27" s="64"/>
+      <c r="K27" s="71" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="C28" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" s="7">
+        <v>4</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H28" s="64"/>
+      <c r="K28" s="73" t="s">
+        <v>206</v>
+      </c>
+      <c r="L28" s="73" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="C29" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="7">
+        <v>5</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="K29" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="L29" s="73" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="C30" s="38"/>
+      <c r="D30" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="7">
+        <v>6</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="K30" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="73" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="71" customFormat="1">
+      <c r="A33" s="51" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="E34" s="75"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="E35" s="75"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="E36" s="75"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="78"/>
+      <c r="E37" s="75"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="C38" s="75"/>
+      <c r="E38" s="75"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="I10:I11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="89" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1C3080-FCA5-4C5F-B176-604DA64226ED}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
+      <c r="K1" s="71" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="115" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="116"/>
+      <c r="B3" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="K3" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="L3" s="71"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
+        <v>3</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="108"/>
+      <c r="K4" s="70" t="s">
+        <v>80</v>
+      </c>
+      <c r="L4" s="70" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="106" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="7">
+        <v>4</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="K5" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="L5" s="70" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="7">
+        <v>5</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="I6" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="K6" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="L6" s="70" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="7">
+        <v>6</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="K7" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="7">
+        <v>7</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
+        <v>8</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="K9" s="71" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="7">
+        <v>9</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="K10" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="L10" s="70" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="69" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="114"/>
+      <c r="D11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="7">
+        <v>10</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="K11" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="28"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="7">
+        <v>11</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="K12" s="76" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="C13" s="108"/>
+      <c r="D13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
+        <v>13</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="75"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="106" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="7">
+        <v>14</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="106" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="106" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="77" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="108"/>
+      <c r="B16" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="107"/>
+      <c r="D16" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="7">
+        <v>15</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="108"/>
+      <c r="H16" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="112"/>
+      <c r="K16" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="107"/>
+      <c r="D17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="7">
+        <v>16</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="28"/>
+      <c r="K17" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="108"/>
+      <c r="B18" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="108"/>
+      <c r="D18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="7">
+        <v>17</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="28"/>
+      <c r="K18" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
+        <v>18</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="K19" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="L19" s="70" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="127" t="s">
+        <v>199</v>
+      </c>
+      <c r="B20" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="7">
+        <v>19</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="128"/>
+      <c r="B21" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="7">
+        <v>20</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="K21" s="71" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="K22" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="70" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="C23" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="K23" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="L23" s="70" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="C24" s="29"/>
+      <c r="D24" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" s="30"/>
+      <c r="H24" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="K24" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="C25" s="31"/>
+      <c r="D25" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="K25" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="L25" s="70" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="C26" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="C27" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="7">
+        <v>3</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="65"/>
+      <c r="H27" s="64"/>
+      <c r="K27" s="71" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="C28" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" s="7">
+        <v>4</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H28" s="64"/>
+      <c r="K28" s="73" t="s">
+        <v>206</v>
+      </c>
+      <c r="L28" s="73" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="C29" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="7">
+        <v>5</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="K29" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="L29" s="73" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="C30" s="38"/>
+      <c r="D30" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="7">
+        <v>6</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="K30" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="73" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="71" customFormat="1">
+      <c r="A33" s="51" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="E34" s="75"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="E35" s="75"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="E36" s="75"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="78"/>
+      <c r="E37" s="75"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="C38" s="75"/>
+      <c r="E38" s="75"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="G15:G16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="89" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31540CD4-B126-4FE7-A4C7-88A45F1D742B}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
+      <c r="K1" s="71" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="115" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="116"/>
+      <c r="B3" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="K3" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="L3" s="71"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
+        <v>3</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="108"/>
+      <c r="K4" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="70" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="106" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="7">
+        <v>4</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="K5" s="79" t="s">
+        <v>80</v>
+      </c>
+      <c r="L5" s="79" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="7">
+        <v>5</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="I6" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="K6" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="7">
+        <v>6</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="K7" s="70" t="s">
+        <v>215</v>
+      </c>
+      <c r="L7" s="70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="7">
+        <v>7</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="K8" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
+        <v>8</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="7">
+        <v>9</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="K10" s="77" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="28"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="7">
+        <v>10</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="K11" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" s="70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="28"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="7">
+        <v>11</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="K12" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="C13" s="108"/>
+      <c r="D13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
+        <v>13</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="K14" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="L14" s="70" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="C15" s="129" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="7">
+        <v>14</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="106" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="126" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="C16" s="130"/>
+      <c r="D16" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="7">
+        <v>15</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="108"/>
+      <c r="H16" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="108"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="C17" s="130"/>
+      <c r="D17" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="7">
+        <v>16</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="28"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="C18" s="130"/>
+      <c r="D18" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="7">
+        <v>17</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="28"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
+        <v>18</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="131" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="7">
+        <v>19</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="132"/>
+      <c r="B21" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="7">
+        <v>20</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="C23" s="18"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="C26" s="51" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="C10:C13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="12.75">
+      <c r="A1" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A3" s="40">
+        <v>1</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="40">
+        <v>2</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A5" s="40">
+        <v>3</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A6" s="40">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A7" s="40">
+        <v>5</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A8" s="40">
+        <v>6</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A9" s="40">
+        <v>7</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A10" s="40">
+        <v>8</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A11" s="40">
+        <v>9</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A12" s="40">
+        <v>10</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A13" s="40">
+        <v>11</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A14" s="40">
+        <v>12</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A15" s="40">
+        <v>13</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A16" s="40">
+        <v>14</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076B43BB-6571-4E49-8DE6-1A5CDADBA573}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="5.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="40">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="40">
+        <v>2</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="54" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="40">
+        <v>3</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="40">
+        <v>4</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="40">
+        <v>5</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="40">
+        <v>6</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="56"/>
+      <c r="D8" s="55" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="40">
+        <v>7</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="56"/>
+      <c r="D9" s="55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="40">
+        <v>8</v>
+      </c>
+      <c r="B10" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="55" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="40">
+        <v>9</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="40">
+        <v>10</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="51" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="40">
+        <v>11</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="40">
+        <v>12</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="40">
+        <v>13</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="40">
+        <v>14</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="51"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A1" s="29"/>
+      <c r="B1" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="30"/>
+      <c r="F1" s="20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A2" s="31"/>
+      <c r="B2" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="7">
+        <v>2</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A4" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="7">
+        <v>3</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="36"/>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A5" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="7">
+        <v>4</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" s="23"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A6" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="7">
+        <v>5</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A7" s="38"/>
+      <c r="B7" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="7">
+        <v>6</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A11" s="41" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A12" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A13" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A14" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="45"/>
+      <c r="D14" s="46" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A15" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1363F85F-892D-48D0-926D-4A26C044C284}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1793,22 +4614,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="111"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="110" t="s">
+      <c r="F1" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="112"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="115" t="s">
         <v>190</v>
       </c>
       <c r="B2" s="62" t="s">
@@ -1831,7 +4652,7 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="114"/>
+      <c r="A3" s="116"/>
       <c r="B3" s="62" t="s">
         <v>65</v>
       </c>
@@ -1851,7 +4672,7 @@
       <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="115" t="s">
+      <c r="I3" s="117" t="s">
         <v>192</v>
       </c>
       <c r="L3" s="10"/>
@@ -1877,12 +4698,12 @@
       <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="109"/>
+      <c r="I4" s="108"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -1901,7 +4722,7 @@
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="108"/>
+      <c r="C6" s="107"/>
       <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
@@ -1924,7 +4745,7 @@
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="108"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
@@ -1941,7 +4762,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="109"/>
+      <c r="C8" s="108"/>
       <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
@@ -1987,7 +4808,7 @@
       <c r="B10" s="88" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="106" t="s">
+      <c r="C10" s="113" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -2014,7 +4835,7 @@
       <c r="B11" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="107"/>
+      <c r="C11" s="114"/>
       <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
@@ -2035,7 +4856,7 @@
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="28"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="108"/>
+      <c r="C12" s="107"/>
       <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
@@ -2050,7 +4871,7 @@
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C13" s="109"/>
+      <c r="C13" s="108"/>
       <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
@@ -2090,13 +4911,13 @@
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="106" t="s">
         <v>102</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2108,22 +4929,22 @@
       <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="116" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="116" t="s">
+      <c r="I15" s="106" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="109"/>
+      <c r="A16" s="108"/>
       <c r="B16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="108"/>
+      <c r="C16" s="107"/>
       <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
@@ -2133,20 +4954,20 @@
       <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="109"/>
+      <c r="G16" s="108"/>
       <c r="H16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="117"/>
+      <c r="I16" s="112"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="116" t="s">
+      <c r="A17" s="106" t="s">
         <v>102</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="108"/>
+      <c r="C17" s="107"/>
       <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
@@ -2163,11 +4984,11 @@
       <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="109"/>
+      <c r="A18" s="108"/>
       <c r="B18" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="109"/>
+      <c r="C18" s="108"/>
       <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
@@ -2315,17 +5136,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A17:A18"/>
     <mergeCell ref="C10:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="C5:C8"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A17:A18"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -2333,1198 +5154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31540CD4-B126-4FE7-A4C7-88A45F1D742B}">
-  <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="110" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="112"/>
-      <c r="K1" s="71" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="113" t="s">
-        <v>190</v>
-      </c>
-      <c r="B2" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="7">
-        <v>1</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="114"/>
-      <c r="B3" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="115" t="s">
-        <v>192</v>
-      </c>
-      <c r="K3" s="71" t="s">
-        <v>207</v>
-      </c>
-      <c r="L3" s="71"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="7">
-        <v>3</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="109"/>
-      <c r="K4" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="L4" s="70" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="4"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="116" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="7">
-        <v>4</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="K5" s="79" t="s">
-        <v>80</v>
-      </c>
-      <c r="L5" s="79" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="7">
-        <v>5</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="63" t="s">
-        <v>202</v>
-      </c>
-      <c r="I6" s="63" t="s">
-        <v>213</v>
-      </c>
-      <c r="K6" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="70" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="7">
-        <v>6</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="K7" s="70" t="s">
-        <v>215</v>
-      </c>
-      <c r="L7" s="70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="109"/>
-      <c r="D8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="7">
-        <v>7</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="K8" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="7">
-        <v>8</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" s="116" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="7">
-        <v>9</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="K10" s="77" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="28"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="7">
-        <v>10</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="K11" s="70" t="s">
-        <v>5</v>
-      </c>
-      <c r="L11" s="70" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="28"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="7">
-        <v>11</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="K12" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="C13" s="109"/>
-      <c r="D13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="7">
-        <v>12</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="K13" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="7">
-        <v>13</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="K14" s="70" t="s">
-        <v>202</v>
-      </c>
-      <c r="L14" s="70" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="C15" s="129" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="7">
-        <v>14</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="116" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="126" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="C16" s="130"/>
-      <c r="D16" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="7">
-        <v>15</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="109"/>
-      <c r="H16" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="I16" s="109"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="C17" s="130"/>
-      <c r="D17" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="7">
-        <v>16</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="28"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="C18" s="130"/>
-      <c r="D18" s="57" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="7">
-        <v>17</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="28"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="7">
-        <v>18</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="131" t="s">
-        <v>189</v>
-      </c>
-      <c r="B20" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="7">
-        <v>19</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="132"/>
-      <c r="B21" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="7">
-        <v>20</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="C23" s="18"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="C26" s="51" t="s">
-        <v>191</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="C10:C13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="4.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="12.75">
-      <c r="A1" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A3" s="40">
-        <v>1</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="40">
-        <v>2</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="40">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="40">
-        <v>4</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A7" s="40">
-        <v>5</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="40">
-        <v>6</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A9" s="40">
-        <v>7</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A10" s="40">
-        <v>8</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A11" s="40">
-        <v>9</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A12" s="40">
-        <v>10</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A13" s="40">
-        <v>11</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A14" s="40">
-        <v>12</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A15" s="40">
-        <v>13</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A16" s="40">
-        <v>14</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>170</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076B43BB-6571-4E49-8DE6-1A5CDADBA573}">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="5.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="40">
-        <v>1</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="53" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="40">
-        <v>2</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="40">
-        <v>3</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="49" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="40">
-        <v>4</v>
-      </c>
-      <c r="B6" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="40">
-        <v>5</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="49" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="40">
-        <v>6</v>
-      </c>
-      <c r="B8" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="55" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="40">
-        <v>7</v>
-      </c>
-      <c r="B9" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="55" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="40">
-        <v>8</v>
-      </c>
-      <c r="B10" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="55" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="40">
-        <v>9</v>
-      </c>
-      <c r="B11" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="40">
-        <v>10</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="51" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="40">
-        <v>11</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>184</v>
-      </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="40">
-        <v>12</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="40">
-        <v>13</v>
-      </c>
-      <c r="B15" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="40">
-        <v>14</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" s="51"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1" s="29"/>
-      <c r="B1" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="20" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="31"/>
-      <c r="B2" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="7">
-        <v>1</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A3" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="7">
-        <v>2</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="7">
-        <v>3</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="36"/>
-      <c r="F4" s="23"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="7">
-        <v>4</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" s="23"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="7">
-        <v>5</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="38"/>
-      <c r="B7" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="7">
-        <v>6</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="43" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A12" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="46" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="46" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A15" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="1" gridLines="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3538,19 +5168,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="111"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="110" t="s">
+      <c r="F1" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="112"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
       <c r="A2" s="89" t="s">
@@ -4021,7 +5651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4042,12 +5672,12 @@
       <c r="C1" s="119"/>
       <c r="D1" s="120"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="110" t="s">
+      <c r="F1" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="112"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="4"/>
@@ -4105,7 +5735,7 @@
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="B5" s="4"/>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -4121,7 +5751,7 @@
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="B6" s="4"/>
-      <c r="C6" s="108"/>
+      <c r="C6" s="107"/>
       <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
@@ -4138,7 +5768,7 @@
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="108"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
@@ -4153,7 +5783,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="109"/>
+      <c r="C8" s="108"/>
       <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
@@ -4186,7 +5816,7 @@
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="B10" s="4"/>
-      <c r="C10" s="116" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -4205,7 +5835,7 @@
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="B11" s="4"/>
-      <c r="C11" s="108"/>
+      <c r="C11" s="107"/>
       <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
@@ -4223,7 +5853,7 @@
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="108"/>
+      <c r="C12" s="107"/>
       <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
@@ -4238,7 +5868,7 @@
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
-      <c r="C13" s="109"/>
+      <c r="C13" s="108"/>
       <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
@@ -4269,7 +5899,7 @@
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="B15" s="4"/>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -4281,14 +5911,14 @@
       <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="116" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="B16" s="4"/>
-      <c r="C16" s="108"/>
+      <c r="C16" s="107"/>
       <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
@@ -4298,13 +5928,13 @@
       <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="109"/>
+      <c r="G16" s="108"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
-      <c r="C17" s="108"/>
+      <c r="C17" s="107"/>
       <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
@@ -4322,7 +5952,7 @@
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
-      <c r="C18" s="109"/>
+      <c r="C18" s="108"/>
       <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
@@ -4409,7 +6039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4423,22 +6053,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="111"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="110" t="s">
+      <c r="F1" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="112"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="106" t="s">
         <v>63</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -4461,7 +6091,7 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="109"/>
+      <c r="A3" s="108"/>
       <c r="B3" s="17" t="s">
         <v>65</v>
       </c>
@@ -4483,7 +6113,7 @@
       <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="116" t="s">
+      <c r="I3" s="106" t="s">
         <v>67</v>
       </c>
       <c r="L3" s="10"/>
@@ -4509,7 +6139,7 @@
       <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="109"/>
+      <c r="I4" s="108"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="17" t="s">
@@ -4518,7 +6148,7 @@
       <c r="B5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -4541,7 +6171,7 @@
       <c r="B6" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="108"/>
+      <c r="C6" s="107"/>
       <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
@@ -4567,7 +6197,7 @@
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="108"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
@@ -4584,7 +6214,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="109"/>
+      <c r="C8" s="108"/>
       <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
@@ -4628,7 +6258,7 @@
       <c r="B10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="116" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -4649,7 +6279,7 @@
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="108"/>
+      <c r="C11" s="107"/>
       <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
@@ -4668,7 +6298,7 @@
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="108"/>
+      <c r="C12" s="107"/>
       <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
@@ -4685,7 +6315,7 @@
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="109"/>
+      <c r="C13" s="108"/>
       <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
@@ -4725,7 +6355,7 @@
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -4737,7 +6367,7 @@
       <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="116" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="2"/>
@@ -4745,7 +6375,7 @@
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="B16" s="4"/>
-      <c r="C16" s="108"/>
+      <c r="C16" s="107"/>
       <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
@@ -4755,14 +6385,14 @@
       <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="109"/>
+      <c r="G16" s="108"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="108"/>
+      <c r="C17" s="107"/>
       <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
@@ -4781,7 +6411,7 @@
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="109"/>
+      <c r="C18" s="108"/>
       <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
@@ -4877,7 +6507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5016,7 +6646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211147EF-ADFD-4B7E-A66F-BDFB2B4B34E8}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5030,19 +6660,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="111"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="110" t="s">
+      <c r="F1" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="112"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="28"/>
@@ -5084,7 +6714,7 @@
       <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="116" t="s">
+      <c r="I3" s="106" t="s">
         <v>67</v>
       </c>
       <c r="L3" s="10"/>
@@ -5110,7 +6740,7 @@
       <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="109"/>
+      <c r="I4" s="108"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="81" t="s">
@@ -5119,7 +6749,7 @@
       <c r="B5" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="106" t="s">
+      <c r="C5" s="113" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -5138,7 +6768,7 @@
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="107"/>
+      <c r="C6" s="114"/>
       <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
@@ -5162,7 +6792,7 @@
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="108"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
@@ -5179,7 +6809,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="109"/>
+      <c r="C8" s="108"/>
       <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
@@ -5223,7 +6853,7 @@
       <c r="B10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="116" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -5248,7 +6878,7 @@
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="108"/>
+      <c r="C11" s="107"/>
       <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
@@ -5269,7 +6899,7 @@
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="108"/>
+      <c r="C12" s="107"/>
       <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
@@ -5286,7 +6916,7 @@
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="109"/>
+      <c r="C13" s="108"/>
       <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
@@ -5338,7 +6968,7 @@
       <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="116" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="2"/>
@@ -5357,7 +6987,7 @@
       <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="109"/>
+      <c r="G16" s="108"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
@@ -5479,7 +7109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5493,22 +7123,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="111"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="110" t="s">
+      <c r="F1" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="112"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="106" t="s">
         <v>94</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -5531,7 +7161,7 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="109"/>
+      <c r="A3" s="108"/>
       <c r="B3" s="17" t="s">
         <v>64</v>
       </c>
@@ -5551,7 +7181,7 @@
       <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="116" t="s">
+      <c r="I3" s="106" t="s">
         <v>67</v>
       </c>
       <c r="L3" s="10"/>
@@ -5577,16 +7207,16 @@
       <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="109"/>
+      <c r="I4" s="108"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="106" t="s">
         <v>95</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -5603,11 +7233,11 @@
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="108"/>
+      <c r="A6" s="107"/>
       <c r="B6" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="108"/>
+      <c r="C6" s="107"/>
       <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
@@ -5631,11 +7261,11 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="109"/>
+      <c r="A7" s="108"/>
       <c r="B7" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="108"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
@@ -5652,7 +7282,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="109"/>
+      <c r="C8" s="108"/>
       <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
@@ -5690,13 +7320,13 @@
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="116" t="s">
+      <c r="A10" s="106" t="s">
         <v>98</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="116" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -5715,11 +7345,11 @@
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="108"/>
+      <c r="A11" s="107"/>
       <c r="B11" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="108"/>
+      <c r="C11" s="107"/>
       <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
@@ -5736,11 +7366,11 @@
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="109"/>
+      <c r="A12" s="108"/>
       <c r="B12" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="108"/>
+      <c r="C12" s="107"/>
       <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
@@ -5761,7 +7391,7 @@
       <c r="B13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="109"/>
+      <c r="C13" s="108"/>
       <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
@@ -5801,13 +7431,13 @@
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="106" t="s">
         <v>102</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -5819,7 +7449,7 @@
       <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="116" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="17" t="s">
@@ -5830,11 +7460,11 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="109"/>
+      <c r="A16" s="108"/>
       <c r="B16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="108"/>
+      <c r="C16" s="107"/>
       <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
@@ -5844,20 +7474,20 @@
       <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="109"/>
+      <c r="G16" s="108"/>
       <c r="H16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="109"/>
+      <c r="I16" s="108"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="116" t="s">
+      <c r="A17" s="106" t="s">
         <v>102</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="108"/>
+      <c r="C17" s="107"/>
       <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
@@ -5873,16 +7503,16 @@
       <c r="H17" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="116" t="s">
+      <c r="I17" s="106" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="109"/>
+      <c r="A18" s="108"/>
       <c r="B18" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="109"/>
+      <c r="C18" s="108"/>
       <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
@@ -5898,7 +7528,7 @@
       <c r="H18" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="I18" s="109"/>
+      <c r="I18" s="108"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
       <c r="A19" s="2"/>
@@ -5994,7 +7624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6013,22 +7643,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="111"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="110" t="s">
+      <c r="F1" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="112"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="115" t="s">
         <v>190</v>
       </c>
       <c r="B2" s="62" t="s">
@@ -6051,7 +7681,7 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="114"/>
+      <c r="A3" s="116"/>
       <c r="B3" s="62" t="s">
         <v>65</v>
       </c>
@@ -6071,7 +7701,7 @@
       <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="115" t="s">
+      <c r="I3" s="117" t="s">
         <v>192</v>
       </c>
       <c r="L3" s="10"/>
@@ -6097,12 +7727,12 @@
       <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="109"/>
+      <c r="I4" s="108"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -6121,7 +7751,7 @@
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="108"/>
+      <c r="C6" s="107"/>
       <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
@@ -6147,7 +7777,7 @@
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="108"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
@@ -6164,7 +7794,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="109"/>
+      <c r="C8" s="108"/>
       <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
@@ -6208,7 +7838,7 @@
       <c r="B10" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="116" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -6229,7 +7859,7 @@
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="28"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="108"/>
+      <c r="C11" s="107"/>
       <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
@@ -6248,7 +7878,7 @@
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="28"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="108"/>
+      <c r="C12" s="107"/>
       <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
@@ -6263,7 +7893,7 @@
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C13" s="109"/>
+      <c r="C13" s="108"/>
       <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
@@ -6303,13 +7933,13 @@
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="106" t="s">
         <v>102</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -6321,22 +7951,22 @@
       <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="116" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="116" t="s">
+      <c r="I15" s="106" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="109"/>
+      <c r="A16" s="108"/>
       <c r="B16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="108"/>
+      <c r="C16" s="107"/>
       <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
@@ -6346,20 +7976,20 @@
       <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="109"/>
+      <c r="G16" s="108"/>
       <c r="H16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="117"/>
+      <c r="I16" s="112"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="116" t="s">
+      <c r="A17" s="106" t="s">
         <v>102</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="108"/>
+      <c r="C17" s="107"/>
       <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
@@ -6376,11 +8006,11 @@
       <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="109"/>
+      <c r="A18" s="108"/>
       <c r="B18" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="109"/>
+      <c r="C18" s="108"/>
       <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
@@ -6614,800 +8244,4 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1C3080-FCA5-4C5F-B176-604DA64226ED}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="110" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="112"/>
-      <c r="K1" s="71" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="113" t="s">
-        <v>190</v>
-      </c>
-      <c r="B2" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="7">
-        <v>1</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="114"/>
-      <c r="B3" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="115" t="s">
-        <v>192</v>
-      </c>
-      <c r="K3" s="71" t="s">
-        <v>207</v>
-      </c>
-      <c r="L3" s="71"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="7">
-        <v>3</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="109"/>
-      <c r="K4" s="70" t="s">
-        <v>80</v>
-      </c>
-      <c r="L4" s="70" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="4"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="116" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="7">
-        <v>4</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="K5" s="70" t="s">
-        <v>204</v>
-      </c>
-      <c r="L5" s="70" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="7">
-        <v>5</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="63" t="s">
-        <v>202</v>
-      </c>
-      <c r="I6" s="63" t="s">
-        <v>213</v>
-      </c>
-      <c r="K6" s="70" t="s">
-        <v>205</v>
-      </c>
-      <c r="L6" s="70" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="7">
-        <v>6</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="K7" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="109"/>
-      <c r="D8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="7">
-        <v>7</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="7">
-        <v>8</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="K9" s="71" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="67" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" s="116" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="7">
-        <v>9</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="K10" s="70" t="s">
-        <v>202</v>
-      </c>
-      <c r="L10" s="70" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="69" t="s">
-        <v>198</v>
-      </c>
-      <c r="C11" s="107"/>
-      <c r="D11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="7">
-        <v>10</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="K11" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="28"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="7">
-        <v>11</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="K12" s="76" t="s">
-        <v>57</v>
-      </c>
-      <c r="L12" s="76" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="C13" s="109"/>
-      <c r="D13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="7">
-        <v>12</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="K13" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" s="70" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="7">
-        <v>13</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="75"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="116" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="116" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="7">
-        <v>14</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="116" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="116" t="s">
-        <v>105</v>
-      </c>
-      <c r="K15" s="77" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="109"/>
-      <c r="B16" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="7">
-        <v>15</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="109"/>
-      <c r="H16" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="I16" s="117"/>
-      <c r="K16" s="70" t="s">
-        <v>5</v>
-      </c>
-      <c r="L16" s="70" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="116" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="108"/>
-      <c r="D17" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="7">
-        <v>16</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="28"/>
-      <c r="K17" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="L17" s="70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="109"/>
-      <c r="B18" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="109"/>
-      <c r="D18" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="7">
-        <v>17</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="28"/>
-      <c r="K18" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="7">
-        <v>18</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="K19" s="70" t="s">
-        <v>202</v>
-      </c>
-      <c r="L19" s="70" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="127" t="s">
-        <v>199</v>
-      </c>
-      <c r="B20" s="69" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="7">
-        <v>19</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="128"/>
-      <c r="B21" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="7">
-        <v>20</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="K21" s="71" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="K22" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="L22" s="70" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="C23" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="K23" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="L23" s="70" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="C24" s="29"/>
-      <c r="D24" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="G24" s="30"/>
-      <c r="H24" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="K24" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L24" s="70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="C25" s="31"/>
-      <c r="D25" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="H25" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="K25" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="L25" s="70" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="C26" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2</v>
-      </c>
-      <c r="F26" s="72" t="s">
-        <v>123</v>
-      </c>
-      <c r="G26" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="H26" s="61" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="C27" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="64"/>
-      <c r="K27" s="71" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="C28" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E28" s="7">
-        <v>4</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H28" s="64"/>
-      <c r="K28" s="73" t="s">
-        <v>206</v>
-      </c>
-      <c r="L28" s="73" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="C29" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D29" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="E29" s="7">
-        <v>5</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G29" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="H29" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="K29" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="L29" s="73" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="C30" s="38"/>
-      <c r="D30" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" s="7">
-        <v>6</v>
-      </c>
-      <c r="F30" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="G30" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="H30" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="K30" s="73" t="s">
-        <v>12</v>
-      </c>
-      <c r="L30" s="73" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="71" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="71" customFormat="1">
-      <c r="A33" s="51" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="51" t="s">
-        <v>218</v>
-      </c>
-      <c r="E34" s="75"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="E35" s="75"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="E36" s="75"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="78"/>
-      <c r="E37" s="75"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="C38" s="75"/>
-      <c r="E38" s="75"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="C5:C8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="89" orientation="landscape" r:id="rId1"/>
-</worksheet>
 </file>